--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.25.xlsx
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.25.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.25.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0025.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0025.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -603,18 +603,18 @@
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dress.â€” 2. The names of the parties.â€” 3. A statement</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing. This Bill formerly consisted of nine parts,â€”1. The ad-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]3. It il</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]3. It il</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L5: isolated marker/symbol line :: g</t>
@@ -628,7 +628,7 @@
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: must containâ€”-...</t>
+          <t>L79: punctuation artifact: repeated periods :: must contain—-...</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,16 +670,8 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” 5. Particular charges in answer to what the Defendant</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dress.â€”2. The names of the parties.â€”3. A statement</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -725,16 +717,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pretends to be his case.â€” 6. An averment that the</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the facts.â€”4. A general charge against the Defendant.</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
@@ -758,12 +742,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,16 +756,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prayer for relief â€” And 9. The prayer for process or</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”5. Particular charges in answer to what the Defendant</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
@@ -819,16 +795,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: must containâ€”â€”â€”</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pretends to be his case.â€”6. An averment that the</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -867,11 +835,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: conscience.â€”7. The interrogatories, which the Defendant</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
@@ -910,11 +874,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: &gt;was bound to answer substantially and literally.â€”8. The</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
@@ -953,11 +913,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prayer for relief.â€”And 9. The prayer for process or</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
@@ -981,12 +937,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -996,11 +952,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: scribed by the following order :â€”</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1029,7 +981,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1039,11 +991,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: must containâ€”-...</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
